--- a/data/trans_dic/P16A20_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A20_2023-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alteración del tiroides últimas 2 semanas</t>
+          <t>Población que ha consumido medicamentos para la alteración del tiroides en las últimas 2 semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,67</t>
+          <t>1,36; 3,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 13,19</t>
+          <t>8,8; 13,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,88</t>
+          <t>6,14; 8,93</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,83</t>
+          <t>0,66; 1,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 40,89</t>
+          <t>7,15; 36,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 24,54</t>
+          <t>3,88; 23,0</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,13</t>
+          <t>0,58; 2,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,28</t>
+          <t>5,57; 9,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,36</t>
+          <t>3,38; 5,26</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,82</t>
+          <t>0,9; 1,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 29,86</t>
+          <t>7,83; 29,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 15,57</t>
+          <t>4,55; 18,42</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alteración del tiroides últimas 2 semanas</t>
+          <t>Población que ha consumido medicamentos para la alteración del tiroides en las últimas 2 semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1972</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1966</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7092; 18852</t>
+          <t>6966; 19249</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1961</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2125</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1989</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>66646; 99206</t>
+          <t>66186; 98071</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1971</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2057</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1982</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>76516; 112422</t>
+          <t>77780; 113108</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2005</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2031</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14649; 41857</t>
+          <t>15062; 41070</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1947</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2034</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1940</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>160645; 914664</t>
+          <t>159943; 808594</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2017</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1993</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>174704; 1111147</t>
+          <t>175843; 1041461</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2017</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2037</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2072</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3872; 13764</t>
+          <t>3762; 14952</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2044</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2081</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1933</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37355; 61233</t>
+          <t>36776; 59507</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2060</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44560; 70075</t>
+          <t>44134; 68769</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2013</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31461; 62875</t>
+          <t>31194; 62374</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2064</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1948</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>287110; 1089467</t>
+          <t>285759; 1089978</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1982</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2033</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 1997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>320677; 1105238</t>
+          <t>323290; 1307597</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A20_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A20_2023-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,75</t>
+          <t>1,22; 3,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,8; 13,04</t>
+          <t>8,42; 11,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 8,93</t>
+          <t>5,71; 7,76</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,79</t>
+          <t>0,73; 1,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 36,15</t>
+          <t>7,21; 9,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 23,0</t>
+          <t>4,06; 5,16</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,31</t>
+          <t>0,7; 2,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,02</t>
+          <t>5,8; 9,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,26</t>
+          <t>3,55; 5,32</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,81</t>
+          <t>1,0; 1,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 29,87</t>
+          <t>7,62; 9,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 18,42</t>
+          <t>4,54; 5,4</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>78912</t>
+          <t>80623</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90583</t>
+          <t>93078</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6966; 19249</t>
+          <t>7035; 19987</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>66186; 98071</t>
+          <t>69061; 95346</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77780; 113108</t>
+          <t>79768; 108449</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25769</t>
+          <t>25545</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>358036</t>
+          <t>175889</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>383804</t>
+          <t>201433</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15062; 41070</t>
+          <t>16281; 39974</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>159943; 808594</t>
+          <t>156412; 201269</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>175843; 1041461</t>
+          <t>178656; 227092</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48079</t>
+          <t>53156</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55764</t>
+          <t>62559</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3762; 14952</t>
+          <t>4962; 17605</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36776; 59507</t>
+          <t>42551; 66844</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44134; 68769</t>
+          <t>51253; 76891</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>47404</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>485027</t>
+          <t>309667</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>530151</t>
+          <t>357071</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31194; 62374</t>
+          <t>35230; 62746</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>285759; 1089978</t>
+          <t>283859; 341149</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>323290; 1307597</t>
+          <t>329018; 390864</t>
         </is>
       </c>
     </row>
